--- a/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
@@ -1062,10 +1062,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>55764</x:v>
+        <x:v>51728</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>46</x:v>
@@ -1118,10 +1118,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>55764</x:v>
+        <x:v>51728</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1174,10 +1174,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>55764</x:v>
+        <x:v>51728</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>46</x:v>
@@ -1230,10 +1230,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>55764</x:v>
+        <x:v>51728</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
         <x:v>46</x:v>
@@ -1286,10 +1286,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>55764</x:v>
+        <x:v>51728</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>56</x:v>
@@ -1398,10 +1398,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>55764</x:v>
+        <x:v>51728</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1454,10 +1454,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>55764</x:v>
+        <x:v>51728</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>56</x:v>
@@ -1510,10 +1510,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>55764</x:v>
+        <x:v>51728</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>46</x:v>
@@ -1566,10 +1566,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>55764</x:v>
+        <x:v>51728</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
         <x:v>56</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
@@ -1062,10 +1062,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>51728</x:v>
+        <x:v>54367</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>46</x:v>
@@ -1118,10 +1118,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>51728</x:v>
+        <x:v>54367</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1174,10 +1174,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>51728</x:v>
+        <x:v>54367</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>46</x:v>
@@ -1230,10 +1230,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>51728</x:v>
+        <x:v>54367</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
         <x:v>46</x:v>
@@ -1286,10 +1286,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>51728</x:v>
+        <x:v>54367</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>56</x:v>
@@ -1398,10 +1398,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>51728</x:v>
+        <x:v>54367</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1454,10 +1454,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>51728</x:v>
+        <x:v>54367</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>56</x:v>
@@ -1510,10 +1510,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>51728</x:v>
+        <x:v>54367</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>46</x:v>
@@ -1566,10 +1566,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>51728</x:v>
+        <x:v>54367</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
         <x:v>56</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
@@ -1062,10 +1062,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>54367</x:v>
+        <x:v>50172</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>46</x:v>
@@ -1118,10 +1118,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>54367</x:v>
+        <x:v>50172</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1174,10 +1174,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>54367</x:v>
+        <x:v>50172</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>46</x:v>
@@ -1230,10 +1230,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>54367</x:v>
+        <x:v>50172</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
         <x:v>46</x:v>
@@ -1286,10 +1286,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>54367</x:v>
+        <x:v>50172</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>56</x:v>
@@ -1398,10 +1398,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>54367</x:v>
+        <x:v>50172</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1454,10 +1454,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>54367</x:v>
+        <x:v>50172</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>56</x:v>
@@ -1510,10 +1510,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>54367</x:v>
+        <x:v>50172</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>46</x:v>
@@ -1566,10 +1566,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>54367</x:v>
+        <x:v>50172</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
         <x:v>56</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
@@ -1062,10 +1062,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>50172</x:v>
+        <x:v>59453</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>46</x:v>
@@ -1118,10 +1118,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>50172</x:v>
+        <x:v>59453</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1174,10 +1174,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>50172</x:v>
+        <x:v>59453</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>46</x:v>
@@ -1230,10 +1230,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>50172</x:v>
+        <x:v>59453</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
         <x:v>46</x:v>
@@ -1286,10 +1286,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>50172</x:v>
+        <x:v>59453</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>56</x:v>
@@ -1398,10 +1398,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>50172</x:v>
+        <x:v>59453</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1454,10 +1454,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>50172</x:v>
+        <x:v>59453</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>56</x:v>
@@ -1510,10 +1510,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>50172</x:v>
+        <x:v>59453</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>46</x:v>
@@ -1566,10 +1566,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>50172</x:v>
+        <x:v>59453</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
         <x:v>56</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
@@ -1062,7 +1062,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>59453</x:v>
+        <x:v>51853</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1121,7 +1121,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>59453</x:v>
+        <x:v>51853</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1174,7 +1174,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>59453</x:v>
+        <x:v>51853</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1230,7 +1230,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>59453</x:v>
+        <x:v>51853</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1286,7 +1286,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>59453</x:v>
+        <x:v>51853</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>59453</x:v>
+        <x:v>51853</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1457,7 +1457,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>59453</x:v>
+        <x:v>51853</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>56</x:v>
@@ -1513,7 +1513,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>59453</x:v>
+        <x:v>51853</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>46</x:v>
@@ -1566,7 +1566,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>59453</x:v>
+        <x:v>51853</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
@@ -1062,7 +1062,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>51853</x:v>
+        <x:v>62619</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1121,7 +1121,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>51853</x:v>
+        <x:v>62619</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1174,7 +1174,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>51853</x:v>
+        <x:v>62619</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1230,7 +1230,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>51853</x:v>
+        <x:v>62619</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1286,7 +1286,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>51853</x:v>
+        <x:v>62619</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>51853</x:v>
+        <x:v>62619</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1457,7 +1457,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>51853</x:v>
+        <x:v>62619</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>56</x:v>
@@ -1513,7 +1513,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>51853</x:v>
+        <x:v>62619</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>46</x:v>
@@ -1566,7 +1566,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>51853</x:v>
+        <x:v>62619</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
@@ -1062,7 +1062,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>62619</x:v>
+        <x:v>65201</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1121,7 +1121,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>62619</x:v>
+        <x:v>65201</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1174,7 +1174,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>62619</x:v>
+        <x:v>65201</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1230,7 +1230,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>62619</x:v>
+        <x:v>65201</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1286,7 +1286,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>62619</x:v>
+        <x:v>65201</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>62619</x:v>
+        <x:v>65201</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1457,7 +1457,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>62619</x:v>
+        <x:v>65201</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>56</x:v>
@@ -1513,7 +1513,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>62619</x:v>
+        <x:v>65201</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>46</x:v>
@@ -1566,7 +1566,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>62619</x:v>
+        <x:v>65201</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
@@ -1062,7 +1062,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>65201</x:v>
+        <x:v>49936</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1121,7 +1121,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>65201</x:v>
+        <x:v>49936</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1174,7 +1174,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>65201</x:v>
+        <x:v>49936</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1230,7 +1230,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>65201</x:v>
+        <x:v>49936</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1286,7 +1286,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>65201</x:v>
+        <x:v>49936</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>65201</x:v>
+        <x:v>49936</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1457,7 +1457,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>65201</x:v>
+        <x:v>49936</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>56</x:v>
@@ -1513,7 +1513,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>65201</x:v>
+        <x:v>49936</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>46</x:v>
@@ -1566,7 +1566,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>65201</x:v>
+        <x:v>49936</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
@@ -1062,7 +1062,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>49936</x:v>
+        <x:v>49180</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1121,7 +1121,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>49936</x:v>
+        <x:v>49180</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1174,7 +1174,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>49936</x:v>
+        <x:v>49180</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1230,7 +1230,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>49936</x:v>
+        <x:v>49180</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1286,7 +1286,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>49936</x:v>
+        <x:v>49180</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>49936</x:v>
+        <x:v>49180</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1457,7 +1457,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>49936</x:v>
+        <x:v>49180</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>56</x:v>
@@ -1513,7 +1513,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>49936</x:v>
+        <x:v>49180</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>46</x:v>
@@ -1566,7 +1566,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>49936</x:v>
+        <x:v>49180</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
@@ -1062,7 +1062,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>49180</x:v>
+        <x:v>54244</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1121,7 +1121,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>49180</x:v>
+        <x:v>54244</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1174,7 +1174,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>49180</x:v>
+        <x:v>54244</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1230,7 +1230,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>49180</x:v>
+        <x:v>54244</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1286,7 +1286,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>49180</x:v>
+        <x:v>54244</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>49180</x:v>
+        <x:v>54244</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1457,7 +1457,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>49180</x:v>
+        <x:v>54244</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>56</x:v>
@@ -1513,7 +1513,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>49180</x:v>
+        <x:v>54244</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>46</x:v>
@@ -1566,7 +1566,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>49180</x:v>
+        <x:v>54244</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
@@ -1062,7 +1062,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>54244</x:v>
+        <x:v>56539</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1121,7 +1121,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>54244</x:v>
+        <x:v>56539</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1174,7 +1174,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>54244</x:v>
+        <x:v>56539</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1230,7 +1230,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>54244</x:v>
+        <x:v>56539</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1286,7 +1286,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>54244</x:v>
+        <x:v>56539</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>54244</x:v>
+        <x:v>56539</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1457,7 +1457,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>54244</x:v>
+        <x:v>56539</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>56</x:v>
@@ -1513,7 +1513,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>54244</x:v>
+        <x:v>56539</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>46</x:v>
@@ -1566,7 +1566,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>54244</x:v>
+        <x:v>56539</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
@@ -1062,7 +1062,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>56539</x:v>
+        <x:v>57271</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1121,7 +1121,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>56539</x:v>
+        <x:v>57271</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1174,7 +1174,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>56539</x:v>
+        <x:v>57271</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1230,7 +1230,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>56539</x:v>
+        <x:v>57271</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1286,7 +1286,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>56539</x:v>
+        <x:v>57271</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>56539</x:v>
+        <x:v>57271</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1457,7 +1457,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>56539</x:v>
+        <x:v>57271</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>56</x:v>
@@ -1513,7 +1513,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>56539</x:v>
+        <x:v>57271</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>46</x:v>
@@ -1566,7 +1566,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>56539</x:v>
+        <x:v>57271</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
